--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutmb-my.sharepoint.com/personal/jaturcin_utmb_edu/Documents/manuscripts/bomv-nhps/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutmb-my.sharepoint.com/personal/jaturcin_utmb_edu/Documents/manuscripts/BOMV model/bomv-nhps/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="454" documentId="8_{9DDA6B01-197A-4C02-97FB-4D22D504E60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EDD851B-10A2-4531-984F-61B30C5C22EE}"/>
+  <xr:revisionPtr revIDLastSave="583" documentId="8_{9DDA6B01-197A-4C02-97FB-4D22D504E60E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{571998CA-677D-45C3-A213-21549A35313F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="5" activeTab="5" xr2:uid="{16B6E53A-F339-424C-9596-069F980B37A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="10" xr2:uid="{16B6E53A-F339-424C-9596-069F980B37A5}"/>
   </bookViews>
   <sheets>
     <sheet name="samplesheet" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2486" uniqueCount="190">
   <si>
     <t>DPI</t>
   </si>
@@ -603,6 +603,21 @@
   <si>
     <t>IL-12/IL-23p40</t>
   </si>
+  <si>
+    <t>Antigen</t>
+  </si>
+  <si>
+    <t>Immunoglobulin</t>
+  </si>
+  <si>
+    <t>Endpoint titer</t>
+  </si>
+  <si>
+    <t>SUDV</t>
+  </si>
+  <si>
+    <t>BDBV</t>
+  </si>
 </sst>
 </file>
 
@@ -5345,16 +5360,19 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9E5D1F-A2CC-4A0A-A1D4-953913B5BD4E}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -5362,352 +5380,1380 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+        <v>186</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
-      <c r="C2" s="1">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1">
         <v>5</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" s="1">
         <v>100</v>
       </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1">
         <v>7</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="1">
         <v>300</v>
       </c>
-      <c r="D4" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>10</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="1">
         <v>12800</v>
       </c>
-      <c r="D5" s="1">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1">
         <v>15</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="1">
         <v>6400</v>
       </c>
-      <c r="D6" s="1">
-        <v>25600</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="1">
         <v>28</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="1">
         <v>1200</v>
       </c>
-      <c r="D7" s="1">
-        <v>25600</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
       </c>
-      <c r="C8" s="1">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="C9" s="1">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1">
         <v>7</v>
       </c>
-      <c r="C10" s="1">
-        <v>100</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="C10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
       </c>
-      <c r="C11" s="1">
-        <v>800</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="1">
         <v>15</v>
       </c>
-      <c r="C12" s="1">
-        <v>3200</v>
-      </c>
-      <c r="D12" s="1">
-        <v>12800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="1">
+        <v>25600</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="1">
         <v>28</v>
       </c>
-      <c r="C13" s="1">
-        <v>800</v>
-      </c>
-      <c r="D13" s="1">
-        <v>6400</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="1">
+        <v>25600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="1">
         <v>0</v>
       </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="1">
         <v>5</v>
       </c>
-      <c r="C15" s="1">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" s="1">
         <v>7</v>
       </c>
-      <c r="C16" s="1">
-        <v>200</v>
-      </c>
-      <c r="D16" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B17" s="1">
         <v>10</v>
       </c>
-      <c r="C17" s="1">
-        <v>1600</v>
-      </c>
-      <c r="D17" s="1">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="1">
         <v>15</v>
       </c>
-      <c r="C18" s="1">
-        <v>2400</v>
-      </c>
-      <c r="D18" s="1">
+      <c r="C18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="1">
         <v>3200</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="1">
         <v>28</v>
       </c>
-      <c r="C19" s="1">
-        <v>400</v>
-      </c>
-      <c r="D19" s="1">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B20" s="1">
         <v>0</v>
       </c>
-      <c r="C20" s="1">
-        <v>0</v>
-      </c>
-      <c r="D20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B21" s="1">
         <v>5</v>
       </c>
-      <c r="C21" s="1">
-        <v>200</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B22" s="1">
         <v>7</v>
       </c>
-      <c r="C22" s="1">
-        <v>400</v>
-      </c>
-      <c r="D22" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B23" s="1">
         <v>10</v>
       </c>
-      <c r="C23" s="1">
-        <v>800</v>
-      </c>
-      <c r="D23" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B24" s="1">
         <v>15</v>
       </c>
-      <c r="C24" s="1">
-        <v>6400</v>
-      </c>
-      <c r="D24" s="1">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="1">
+        <v>12800</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B25" s="1">
         <v>28</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="1">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="1">
+        <v>5</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="1">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="1">
+        <v>10</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" s="1">
         <v>1600</v>
       </c>
-      <c r="D25" s="1">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="1">
+        <v>15</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="1">
+        <v>28</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E31" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="1">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="1">
+        <v>5</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="1">
+        <v>7</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="1">
+        <v>10</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="1">
+        <v>15</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="1">
+        <v>28</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="1">
+        <v>5</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="1">
+        <v>7</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="1">
+        <v>10</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="1">
+        <v>15</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" s="1">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="1">
+        <v>28</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" s="1">
         <v>1600</v>
       </c>
     </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="1">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="1">
+        <v>5</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="1">
+        <v>7</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="1">
+        <v>10</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="1">
+        <v>15</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="1">
+        <v>28</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1">
+        <v>0</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="1">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="1">
+        <v>0</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="1">
+        <v>0</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="1">
+        <v>28</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" s="1">
+        <v>28</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="1">
+        <v>28</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E56" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="1">
+        <v>28</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="1">
+        <v>0</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="1">
+        <v>0</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="1">
+        <v>0</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="1">
+        <v>0</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="1">
+        <v>28</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" s="1">
+        <v>28</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="1">
+        <v>28</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="1">
+        <v>28</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="1">
+        <v>0</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B67" s="1">
+        <v>0</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" s="1">
+        <v>0</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="1">
+        <v>0</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="1">
+        <v>28</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E70" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B71" s="1">
+        <v>28</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E71" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="1">
+        <v>28</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E72" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="1">
+        <v>28</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E73" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" s="1">
+        <v>0</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B75" s="1">
+        <v>0</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="1">
+        <v>0</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" s="1">
+        <v>0</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B78" s="1">
+        <v>28</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E78" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B79" s="1">
+        <v>28</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E79" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="1">
+        <v>28</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" s="1">
+        <v>28</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E81" s="1">
+        <v>800</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D26">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F26">
     <sortCondition ref="A1:A26"/>
   </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
